--- a/gorevler/ekler/aicore-crm-listesi/AICore_Urun_Listesi_CRM.xlsx
+++ b/gorevler/ekler/aicore-crm-listesi/AICore_Urun_Listesi_CRM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AICore Ürünleri" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ağırlıklandırma" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AICore Ürünleri" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ağırlıklandırma" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1016,128 +1016,145 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TalentCoreAI</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Tüm ekiplerinizin yetkinliğini kanıta dayalı tek bir haritada toplar, tek kişiye bağlı kalan uzmanlığı önceden gösterir. Eğitim, yedek uzman ve kapasite ihtiyacı yalnızca kayıt sayısından değil, çözümlerin karmaşıklığından ve kalitesinden çıkar. Son karar her zaman yöneticide kalır. Sayfa: https://www.servicecore.com.tr/aicore/talentcore</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>SCAITLN</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>— HİZMET VE DESTEK PAKETLERİ —</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr"/>
-      <c r="C34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>AICORE Launch Ready Paketi</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>AICore eklentileri için anahtar teslim kurulum hizmeti. Yapay zekâ sunucusunun kurulumundan kurumun kendi verisiyle kalibrasyona, ekip eğitiminden gözetimli canlıya alışa kadar uçtan uca devreye alma. Tipik süre 2-4 hafta; sonraki eklentiler aynı altyapıya çok daha hızlı eklenir. Sayfa: https://www.servicecore.com.tr/hizmetler/setup/aicore-launch-ready</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>SCAILRCP</t>
-        </is>
-      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>AICORE Cloud Ready Paketi</t>
+          <t>AICORE Launch Ready Paketi</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Maskeli Bulut modunda AICore kurulum hizmeti. Kurum ortamına dil modeli kurulmaz; GPU'suz hafif uygulama sunucusu, kişisel verileri denetlenebilir şekilde maskeleyen katman, kalibrasyon ve eğitimle 1-2 haftada devreye alma. Bulut kullanım (token) maliyeti kurumun kendi API hesabına aittir. Sayfa: https://www.servicecore.com.tr/hizmetler/setup/aicore-cloud-ready</t>
+          <t>AICore eklentileri için anahtar teslim kurulum hizmeti. Yapay zekâ sunucusunun kurulumundan kurumun kendi verisiyle kalibrasyona, ekip eğitiminden gözetimli canlıya alışa kadar uçtan uca devreye alma. Tipik süre 2-4 hafta; sonraki eklentiler aynı altyapıya çok daha hızlı eklenir. Sayfa: https://www.servicecore.com.tr/hizmetler/setup/aicore-launch-ready</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>SCAICRCP</t>
+          <t>SCAILRCP</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>AICORE Quick Start Konfigürasyon Paketi</t>
+          <t>AICORE Cloud Ready Paketi</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Mevcut AICore altyapısına sonraki her eklentinin devreye alma paketi. Altyapı işi tekrarlanmaz: eklenti kurulumu, varsa ek erişimlerin bağlanması, eklentiye özel kalibrasyon, doğrulama setinin genişletilmesi ve odaklı eğitim — tipik 2-5 gün. İlk kurulum Launch Ready/Cloud Ready ile yapılır; sonraki her eklenti Quick Start ile eklenir. Sayfa: https://www.servicecore.com.tr/hizmetler/setup/aicore-quick-start</t>
+          <t>Maskeli Bulut modunda AICore kurulum hizmeti. Kurum ortamına dil modeli kurulmaz; GPU'suz hafif uygulama sunucusu, kişisel verileri denetlenebilir şekilde maskeleyen katman, kalibrasyon ve eğitimle 1-2 haftada devreye alma. Bulut kullanım (token) maliyeti kurumun kendi API hesabına aittir. Sayfa: https://www.servicecore.com.tr/hizmetler/setup/aicore-cloud-ready</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>SCAIQSCP</t>
+          <t>SCAICRCP</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AICORE Silver Destek Paketi</t>
+          <t>AICORE Quick Start Konfigürasyon Paketi</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>AICore eklentileri için temel yıllık bakım. Yıllık 15 ticket, 5x8 kapsam, sürüm güncellemeleri + güncelleme sonrası otomatik doğrulama, yılda 1 yeniden kalibrasyon ve yıllık sağlık raporu. Sayfa: https://www.servicecore.com.tr/hizmetler/support/aicore-destek</t>
+          <t>Mevcut AICore altyapısına sonraki her eklentinin devreye alma paketi. Altyapı işi tekrarlanmaz: eklenti kurulumu, varsa ek erişimlerin bağlanması, eklentiye özel kalibrasyon, doğrulama setinin genişletilmesi ve odaklı eğitim — tipik 2-5 gün. İlk kurulum Launch Ready/Cloud Ready ile yapılır; sonraki her eklenti Quick Start ile eklenir. Sayfa: https://www.servicecore.com.tr/hizmetler/setup/aicore-quick-start</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>SCAISSP</t>
+          <t>SCAIQSCP</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>AICORE Gold Destek Paketi</t>
+          <t>AICORE Silver Destek Paketi</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Birden çok AICore eklentisi kullanan kurumlar için yıllık bakım. Yıllık 30 ticket, 5x8 kapsam + telefon desteği, yılda 2 yeniden kalibrasyon, çeyreklik sağlık raporu ve AI Health-Check. Sayfa: https://www.servicecore.com.tr/hizmetler/support/aicore-destek</t>
+          <t>AICore eklentileri için temel yıllık bakım. Yıllık 15 ticket, 5x8 kapsam, sürüm güncellemeleri + güncelleme sonrası otomatik doğrulama, yılda 1 yeniden kalibrasyon ve yıllık sağlık raporu. Sayfa: https://www.servicecore.com.tr/hizmetler/support/aicore-destek</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>SCAIGSP</t>
+          <t>SCAISSP</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AICORE Platinum Destek Paketi</t>
+          <t>AICORE Gold Destek Paketi</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Yapay zekâyı iş akışının parçası yapmış kurumlar için yıllık bakım. Yıllık 60 ticket, 7x8 kapsam + anlık mesaj, yılda 4 yeniden kalibrasyon, aylık sağlık raporu, yüksek öncelikli müdahale ve model performansı izleme. Sayfa: https://www.servicecore.com.tr/hizmetler/support/aicore-destek</t>
+          <t>Birden çok AICore eklentisi kullanan kurumlar için yıllık bakım. Yıllık 30 ticket, 5x8 kapsam + telefon desteği, yılda 2 yeniden kalibrasyon, çeyreklik sağlık raporu ve AI Health-Check. Sayfa: https://www.servicecore.com.tr/hizmetler/support/aicore-destek</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>SCAIPSP</t>
+          <t>SCAIGSP</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>AICORE Platinum Destek Paketi</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Yapay zekâyı iş akışının parçası yapmış kurumlar için yıllık bakım. Yıllık 60 ticket, 7x8 kapsam + anlık mesaj, yılda 4 yeniden kalibrasyon, aylık sağlık raporu, yüksek öncelikli müdahale ve model performansı izleme. Sayfa: https://www.servicecore.com.tr/hizmetler/support/aicore-destek</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>SCAIPSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
           <t>AICORE Mission Critical Destek Paketi</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Yapay zekâsı kesintiye tahammülü olmayan kurumlar için en üst kademe. Yıllık 60 ticket, 7x24 kesintisiz kapsam, sınırsız yeniden kalibrasyon, aylık rapor + dönemsel değerlendirme ve adanmış yapay zekâ uzmanı. Sayfa: https://www.servicecore.com.tr/hizmetler/support/aicore-destek</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>SCAIMCSP</t>
         </is>
@@ -1154,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1628,53 +1645,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DocCoreAI</t>
+          <t>TalentCoreAI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SCAIDOC</t>
+          <t>SCAITLN</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2.3X</t>
+          <t>2.5X</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
+          <t>4.0X</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
           <t>3.0X</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>3.0X</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Doküman kaynak erişimi kurulumu; işleme hattı ortak</t>
+          <t>ÖNERİ, onay bekliyor: geniş kapsam (yetkinlik haritası, bağımlılık riski, atama ve gelişim önerisi); kayıt geçmişi ile eğitim, sertifika ve izin verisi entegrasyonu</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ClassifyCoreAI</t>
+          <t>DocCoreAI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SCAICLS</t>
+          <t>SCAIDOC</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1703,19 +1720,19 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Kategori/atama eğitimi + müşteri şemasına uyarlama</t>
+          <t>Doküman kaynak erişimi kurulumu; işleme hattı ortak</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PredictCoreAI</t>
+          <t>ClassifyCoreAI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SCAIPRD</t>
+          <t>SCAICLS</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1744,19 +1761,19 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Tahmin kalitesi izleme ister</t>
+          <t>Kategori/atama eğitimi + müşteri şemasına uyarlama</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ReportCoreAI</t>
+          <t>PredictCoreAI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SCAIRPT</t>
+          <t>SCAIPRD</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1766,11 +1783,11 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2.2X</t>
+          <t>2.3X</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1780,75 +1797,75 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>2.0X</t>
+          <t>3.0X</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Yönetici görünürlüğü yüksek; rapor şemasına uyarlama</t>
+          <t>Tahmin kalitesi izleme ister</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ReplyCoreAI</t>
+          <t>ReportCoreAI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SCAIRPL</t>
+          <t>SCAIRPT</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
+          <t>2.2X</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>3.0X</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
           <t>2.0X</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>2.0X</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>2.0X</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Yüksek görünür değer; teknik olarak hafif</t>
+          <t>Yönetici görünürlüğü yüksek; rapor şemasına uyarlama</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AssetCoreAI</t>
+          <t>ReplyCoreAI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SCAIAST</t>
+          <t>SCAIRPL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -1857,29 +1874,29 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>3.0X</t>
+          <t>2.0X</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>3.0X</t>
+          <t>2.0X</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Telemetri kaynaklarına bağımlı</t>
+          <t>Yüksek görünür değer; teknik olarak hafif</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ImpactCoreAI</t>
+          <t>AssetCoreAI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SCAIIMP</t>
+          <t>SCAIAST</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1889,11 +1906,11 @@
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>1.9X</t>
+          <t>2.0X</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1903,24 +1920,24 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>2.0X</t>
+          <t>3.0X</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Varlık ilişkisi verisine bağımlı</t>
+          <t>Telemetri kaynaklarına bağımlı</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FlowCoreAI</t>
+          <t>ImpactCoreAI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SCAIFLW</t>
+          <t>SCAIIMP</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1949,19 +1966,19 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Yapılandırma düzeyi yazma; onay akışı şart</t>
+          <t>Varlık ilişkisi verisine bağımlı</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ShiftCoreAI</t>
+          <t>FlowCoreAI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SCAISHF</t>
+          <t>SCAIFLW</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1990,19 +2007,19 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>İK/vardiya verisi entegrasyonu</t>
+          <t>Yapılandırma düzeyi yazma; onay akışı şart</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AuditCoreAI</t>
+          <t>ShiftCoreAI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SCAIAUD</t>
+          <t>SCAISHF</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2031,19 +2048,19 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Periyodik denetim; orta kapsam</t>
+          <t>İK/vardiya verisi entegrasyonu</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BudgetCoreAI</t>
+          <t>AuditCoreAI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SCAIBDG</t>
+          <t>SCAIAUD</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2072,60 +2089,60 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Finans verisi entegrasyonu</t>
+          <t>Periyodik denetim; orta kapsam</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MergeCoreAI</t>
+          <t>BudgetCoreAI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SCAIMRG</t>
+          <t>SCAIBDG</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>1.7X</t>
+          <t>1.9X</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
+          <t>3.0X</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
           <t>2.0X</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>2.0X</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Motor hazır; sınırlı yüzey</t>
+          <t>Finans verisi entegrasyonu</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PriorityCoreAI</t>
+          <t>MergeCoreAI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SCAIPRI</t>
+          <t>SCAIMRG</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2154,19 +2171,19 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Dar kapsam, hafif</t>
+          <t>Motor hazır; sınırlı yüzey</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KBCoreAI</t>
+          <t>PriorityCoreAI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SCAIKBC</t>
+          <t>SCAIPRI</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2195,19 +2212,19 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Bilgi bankası taraması; orta kapsam</t>
+          <t>Dar kapsam, hafif</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VisionCoreAI</t>
+          <t>KBCoreAI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SCAIVSN</t>
+          <t>SCAIKBC</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2236,19 +2253,19 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Görsel okuma; mevcut yeteneğin ürünleşmesi</t>
+          <t>Bilgi bankası taraması; orta kapsam</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ContractCoreAI</t>
+          <t>VisionCoreAI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SCAICNT</t>
+          <t>SCAIVSN</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2277,19 +2294,19 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Doküman deposu erişimi; orta</t>
+          <t>Görsel okuma; mevcut yeteneğin ürünleşmesi</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ProjectCoreAI</t>
+          <t>ContractCoreAI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SCAIPRJ</t>
+          <t>SCAICNT</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2318,23 +2335,23 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Proje verisi analizi; orta</t>
+          <t>Doküman deposu erişimi; orta</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VendorCoreAI</t>
+          <t>ProjectCoreAI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SCAIVND</t>
+          <t>SCAIPRJ</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
         <v>2</v>
@@ -2344,7 +2361,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>1.3X</t>
+          <t>1.7X</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -2359,19 +2376,19 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Dar kapsam</t>
+          <t>Proje verisi analizi; orta</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CoachCoreAI</t>
+          <t>VendorCoreAI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SCAICCH</t>
+          <t>SCAIVND</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2407,53 +2424,53 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SentimentCoreAI</t>
+          <t>CoachCoreAI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SCAISNT</t>
+          <t>SCAICCH</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>1.0X</t>
+          <t>1.3X</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>1.0X</t>
+          <t>2.0X</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>1.0X</t>
+          <t>2.0X</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Basit analiz; taban ürün</t>
+          <t>Dar kapsam</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ToneCoreAI</t>
+          <t>SentimentCoreAI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SCAITON</t>
+          <t>SCAISNT</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2489,12 +2506,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TranslateCoreAI</t>
+          <t>ToneCoreAI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SCAITRN</t>
+          <t>SCAITON</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2523,33 +2540,74 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
+          <t>Basit analiz; taban ürün</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TranslateCoreAI</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SCAITRN</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>1.0X</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>1.0X</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>1.0X</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
           <t>Basit çeviri katmanı; taban ürün</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Model — üç ayrı çarpan, üç ayrı fiyat kalemi:</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>· Lisans Çarpanı = (0,5·Değer + 0,3·Kurulum + 0,2·Bakım) / taban → modül lisans fiyatı = lisans tabanı × bu çarpan.</t>
+          <t>Model — üç ayrı çarpan, üç ayrı fiyat kalemi:</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>· Kurulum Hizmeti Çarpanı = Kurulum Zorluğu / taban → modül kurulum bedeli = kurulum tabanı (Launch Ready veya Cloud Ready) × bu çarpan.</t>
+          <t>· Lisans Çarpanı = (0,5·Değer + 0,3·Kurulum + 0,2·Bakım) / taban → modül lisans fiyatı = lisans tabanı × bu çarpan.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>· Kurulum Hizmeti Çarpanı = Kurulum Zorluğu / taban → modül kurulum bedeli = kurulum tabanı (Launch Ready veya Cloud Ready) × bu çarpan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>· Destek Hizmeti Çarpanı = Bakım Zorluğu / taban → modülün yıllık destek payı = destek tabanı (Silver/Gold/Platinum) × bu çarpan; sözleşme tek, fiyat toplamdan.</t>
         </is>
